--- a/docs/开放平台分层组件清单_v1.2.1.xlsx
+++ b/docs/开放平台分层组件清单_v1.2.1.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="分层组件清单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="分层汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="workhub 对接计划" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'分层组件清单'!$A$1:$J$182</definedName>
@@ -45,7 +46,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +118,11 @@
         <fgColor rgb="FFfef3c7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFfde68a"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -144,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -229,6 +235,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10320,4 +10359,741 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>对接类别</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>对接项（接口 / 能力）</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>对接要点 / 说明</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>依赖现状</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>清单引用（Sheet1「分层组件清单」编号 → 行号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>准入准备</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>应用注册与 API Key 下发</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>经管理 Portal 注册应用并签发 API Key（sha256 入库、明文仅返回一次）；workhub 侧配置凭证</t>
+        </is>
+      </c>
+      <c r="E2" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F2" s="32" t="inlineStr">
+        <is>
+          <t>已落地（流程文档待补）</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>L0-18（第 19 行）；L1-03（第 22 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="30" t="inlineStr">
+        <is>
+          <t>准入准备</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>数字员工身份与权限对接</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>请求头注入 X-User-Id / X-Tenant-Id / X-User-Roles 等身份头，X-Auth-System=digital_employee；AUTHZ deny-overrides，越权统一 100403</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>已落地（角色→动作映射待补齐）</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>L1-27（第 46 行）；L1-28（第 47 行）；L1-29（第 48 行）；L1-30（第 49 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>准入准备</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>限流与配额确认</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>应用绑定 QPS + 日额度，超限返回 100429；数字员工侧需做退避重试</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>已落地（进程内实现，共享化改造中）</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>L1-05（第 24 行）；L1-09（第 28 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>平台机制</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>统一响应协议</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>所有响应为 errCode / errMsg / data / traceId 统一壳；成功 000000，参数错误 100001</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>已落地</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>L1-07（第 26 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>平台机制</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Trace 全链路追踪</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>复用 / 回写 X-Request-Id 与 X-Trace-Id，响应体带 traceId；日志中心按 traceId 检索</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>已落地</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>L1-08（第 27 行）；X-14（第 168 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>接入形态</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Python SDK 接入</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ikc-open-platform-sdk 0.2.0（httpx 客户端 + 统一壳解包 + 错误映射），主推集成形态</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>已可用（制品重打包待办）</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>L1-14（第 33 行）；L1-15（第 34 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>接入形态</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>MCP 工具接入</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ikc-op-mcp（15 工具，stdio NDJSON JSON-RPC 2.0）——数字员工工具调用首选形态</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>已可用</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>L0-11（第 12 行）；L1-17（第 36 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>接入形态</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CLI 接入（调试/运维）</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ikc-op 15 子命令（kb-* / doc-* / parse-* / search-* / sys-*），用于联调与排障</t>
+        </is>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>已可用</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>L0-12（第 13 行）；L1-16（第 35 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>接入形态</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Java SDK 接入（规划）</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>workhub Java 侧集成（Maven 坐标建议 io.openikc:ikc-open-platform-sdk）</t>
+        </is>
+      </c>
+      <c r="E10" s="36" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>待建</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>L0-13（第 14 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>接入形态</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>接入指南与示例工程</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>REST / SDK / MCP / CLI 四形态接入指南 + 建库→接文档→解析轮询→检索 示例</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>待补</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>L0-15（第 16 行）；L0-16（第 17 行）；L0-17（第 18 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>知识库能力</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>知识库创建 / 更新</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/v1/knowledge-bases/create、/update；库形态 text / wiki / graph</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>链路已落地</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>L3-03（第 73 行）；L3-01（第 71 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>知识库能力</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>知识库查询</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/v1/knowledge-bases/query、GET /api/v1/knowledge-bases/{kb_id}</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>已落地</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>L3-03（第 73 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>文档与解析</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>文档接入（异步）</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/v1/knowledge-documents/ingest、/ingest-and-parse（executeMode=async 提交 + 轮询状态）；上传通路 501001→pyuploadX 待落地</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>异步透传已落地；上传占位待落地</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>L3-03（第 73 行）；L2-01（第 56 行）；L2-02（第 57 行）；L3-31（第 101 行）；L4-12（第 124 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>文档与解析</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>解析任务与结果获取</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/v1/knowledge-documents/parse + GET parse-result/query、issue-download-ticket、download（产物 text / markdown / json / wiki jsonl / graph jsonl）</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>平台侧占位（501001）待落地</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>L3-31（第 101 行）；L3-32（第 102 行）；L3-33（第 103 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>文档与解析</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>文档查询</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/v1/knowledge-documents/{doc_id}</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>已落地</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>L3-03（第 73 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="39" t="inlineStr">
+        <is>
+          <t>检索能力</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>统一检索（RAG）</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/v1/knowledge-search/universal-search（Gateway 同步直连 Universal Retriever，不经调度层）</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>检索服务 WIP</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>L3-19（第 89 行）；L3-22（第 92 行）；L3-21（第 91 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>检索能力</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>深度检索（Agentic RAG）</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/v1/knowledge-search/deep-search（多轮检索 + 引用回答），数字员工问答主链路</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>待落地</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>L3-25（第 95 行）；V1.2-03（第 180 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>检索能力</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>兼容别名 /query</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/v1/knowledge-search/query（指向 universal-search，存量调用兼容）</t>
+        </is>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>已接线</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>L3-22（第 92 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>检索能力</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>GraphRAG / OAG 本体增强检索（规划）</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>依赖本体构建引擎 + 本体存储落地后提供图谱/本体增强检索，权限可按库过滤</t>
+        </is>
+      </c>
+      <c r="E20" s="36" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>图中规划（待排期）</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>V1.2-01（第 178 行）；V1.2-03（第 180 行）；V1.2-04（第 181 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>口径：从数字员工类平台应用（workhub）视角整理的对接清单，覆盖 准入准备 / 平台机制 / 接入形态 / 知识库 / 文档与解析 / 检索 六类；「清单引用」为同工作簿 Sheet1「分层组件清单」的编号与行号（第 1 行为表头，数据自第 2 行起），行号可直接定位对应条目的现状与时间安排。系统侧选择 X-Auth-System=digital_employee（内置授权系统）；对接前先完成应用注册与 API Key 下发（序号 1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A22:G24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>